--- a/data/trans_orig/IP07_C12_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07_C12_2023-Estudios-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de cansancio para realizar lo que le gusta en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según la frecuencia de haber estado demasiado cansado/a para disfrutar de las cosas que le gusta hacer, percibida por el/la menor en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,107 +720,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>653</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3686</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,26%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3469</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>4,63%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>29,71%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>24,87%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>2964</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>653</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3518</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>897</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3183</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>801</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5543</t>
+          <t>3858</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1579</t>
+          <t>1698</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,14%</t>
         </is>
       </c>
     </row>
@@ -946,107 +946,107 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>876</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4622</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>5,23%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>27,57%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>783</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>876</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>4492</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>4,68%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>4487</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>2,85%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>26,81%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>783</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>3213</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>14,61%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2771</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6327</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>16,53%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,75%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>37,75%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1872</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>364</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4639</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>15,09%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,93%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>37,39%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2723</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>345</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6566</t>
+          <t>5358</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>4595</t>
+          <t>4614</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1812</t>
+          <t>1823</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8964</t>
+          <t>8772</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>28,56%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12219</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8643</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>15068</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>72,89%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>51,56%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>89,89%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>9166</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>5697</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>11402</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>73,88%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>45,92%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>91,9%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>12385</t>
+          <t>10659</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8332</t>
+          <t>7085</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14853</t>
+          <t>13061</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>50,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>21551</t>
+          <t>22879</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16962</t>
+          <t>17887</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25367</t>
+          <t>26418</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,01%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>16763</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>16763</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>16763</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>12407</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>12407</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>12407</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16754</t>
+          <t>13950</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16754</t>
+          <t>13950</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16754</t>
+          <t>13950</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>29162</t>
+          <t>30713</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>29162</t>
+          <t>30713</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>29162</t>
+          <t>30713</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5071</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1047</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>992</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3946</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3384</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5154</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>371</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5366</t>
+          <t>5634</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2143</t>
+          <t>2261</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>584</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6383</t>
+          <t>7143</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2396</t>
+          <t>2270</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>574</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6778</t>
+          <t>6966</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4539</t>
+          <t>4532</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>1677</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9951</t>
+          <t>10096</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>999</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3267</t>
+          <t>4841</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>359</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6657</t>
+          <t>1810</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1495</t>
+          <t>1357</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6948</t>
+          <t>6736</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>37661</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>25804</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>53221</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>18,8%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>12,88%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>26,57%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>52213</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>27783</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>94011</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>32,77%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>17,44%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>59,01%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38073</t>
+          <t>29484</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25764</t>
+          <t>21339</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56301</t>
+          <t>39530</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>90286</t>
+          <t>67145</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>63595</t>
+          <t>51737</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>159648</t>
+          <t>86623</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>25,25%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>158458</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>142056</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>170439</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>79,1%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>70,91%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>85,08%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>151</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>103494</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>63025</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>126989</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>64,96%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>39,56%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>79,71%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>160242</t>
+          <t>109565</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>143277</t>
+          <t>99753</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>172605</t>
+          <t>118194</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>263736</t>
+          <t>268023</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>198480</t>
+          <t>249223</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>290267</t>
+          <t>284103</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>82,83%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>200333</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>200333</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>200333</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>195</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>159313</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>159313</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>159313</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>202700</t>
+          <t>142669</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>202700</t>
+          <t>142669</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>202700</t>
+          <t>142669</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>362013</t>
+          <t>343002</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>362013</t>
+          <t>343002</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>362013</t>
+          <t>343002</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2451</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>596</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>6745</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>4,62%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>12,73%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>590</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>3654</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>2701</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>9,43%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>2404</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>595</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>6540</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>4,56%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2994</t>
+          <t>3043</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>993</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>7687</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2416</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>6889</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>4,56%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>13,0%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>1445</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>4775</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>3,73%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>12,32%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2369</t>
+          <t>1672</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>389</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8593</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>3815</t>
+          <t>4089</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1357</t>
+          <t>1146</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9798</t>
+          <t>10650</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>11,33%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>7254</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>3653</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>12393</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>13,69%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>6,89%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>23,38%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>4623</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>2075</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>9171</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>11,93%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>5,35%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>23,67%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7229</t>
+          <t>4861</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3797</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12478</t>
+          <t>9111</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>11853</t>
+          <t>12115</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7144</t>
+          <t>7231</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18025</t>
+          <t>18492</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,68%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>40882</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>35344</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>45641</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>77,13%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>66,68%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>86,11%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>32094</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>27415</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>35060</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>82,82%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>70,75%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>90,47%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>40690</t>
+          <t>33844</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34220</t>
+          <t>29065</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>45645</t>
+          <t>37401</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>72784</t>
+          <t>74727</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>65658</t>
+          <t>66480</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>78634</t>
+          <t>80846</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>86,03%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>53004</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>53004</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>53004</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>38752</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>38752</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>38752</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>52693</t>
+          <t>40969</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>52693</t>
+          <t>40969</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>52693</t>
+          <t>40969</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>91445</t>
+          <t>93974</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>91445</t>
+          <t>93974</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>91445</t>
+          <t>93974</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>4765</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>434</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>5007</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>2,38%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>1637</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>362</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5074</t>
+          <t>4668</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2591</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>656</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6660</t>
+          <t>7018</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -2879,72 +2879,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>5609</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2220</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>11864</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>4,39%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>3450</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>8147</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>3,87%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>5662</t>
+          <t>3664</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2171</t>
+          <t>1380</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10736</t>
+          <t>8596</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>9112</t>
+          <t>9273</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4608</t>
+          <t>4820</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>15614</t>
+          <t>15805</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>4291</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>990</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5521</t>
+          <t>11337</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4232</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>497</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11076</t>
+          <t>5069</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6093</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2426</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>12809</t>
+          <t>14202</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>47686</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>34801</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>65589</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>17,66%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>12,88%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>24,28%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>58708</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>32701</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>113487</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>27,89%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>15,54%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>53,92%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>48025</t>
+          <t>36188</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>34990</t>
+          <t>26785</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>68256</t>
+          <t>47813</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>106734</t>
+          <t>83875</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>78553</t>
+          <t>66607</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>178588</t>
+          <t>105456</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>22,55%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>211560</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>192651</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>225060</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>78,33%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>71,33%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>83,32%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>210</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>144753</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>93502</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>170004</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>68,78%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>44,42%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>80,77%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>213317</t>
+          <t>154068</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>191787</t>
+          <t>143121</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>227517</t>
+          <t>164608</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>358070</t>
+          <t>365627</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>288306</t>
+          <t>343993</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>385157</t>
+          <t>384197</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>59,74%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>82,15%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>272147</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>272147</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>272147</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
